--- a/Assets/Excels/RaftConfigTemplate.xlsx
+++ b/Assets/Excels/RaftConfigTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamejam\ceshi\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4331E26F-EB08-4B68-937F-6FA07428E0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F1DFD8-AE9C-471E-8419-6FF3834338C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1215,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excels/RaftConfigTemplate.xlsx
+++ b/Assets/Excels/RaftConfigTemplate.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamejam\ceshi\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F1DFD8-AE9C-471E-8419-6FF3834338C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D0D462-A87E-41AA-825B-E21A464F467C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="building" sheetId="1" r:id="rId1"/>
     <sheet name="item" sheetId="2" r:id="rId2"/>
     <sheet name="refresh" sheetId="3" r:id="rId3"/>
     <sheet name="survival" sheetId="4" r:id="rId4"/>
+    <sheet name="synthesis" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="91">
+  <si>
+    <t>建筑唯一ID</t>
+  </si>
+  <si>
+    <t>建筑显示名</t>
+  </si>
+  <si>
+    <t>消耗道具ID</t>
+  </si>
+  <si>
+    <t>消耗数量</t>
+  </si>
   <si>
     <t>buildingId</t>
   </si>
@@ -47,22 +60,34 @@
     <t>displayName</t>
   </si>
   <si>
-    <t>costItemType</t>
+    <t>costItemTypeId</t>
   </si>
   <si>
     <t>costAmount</t>
   </si>
   <si>
-    <t>raft_foundation</t>
-  </si>
-  <si>
     <t>木筏地基</t>
   </si>
   <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>itemType</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>道具数字ID</t>
+  </si>
+  <si>
+    <t>道具显示名</t>
+  </si>
+  <si>
+    <t>恢复饥饿值</t>
+  </si>
+  <si>
+    <t>恢复口渴值</t>
+  </si>
+  <si>
+    <t>itemTypeId</t>
   </si>
   <si>
     <t>hungerRestore</t>
@@ -71,7 +96,7 @@
     <t>thirstRestore</t>
   </si>
   <si>
-    <t>Beet</t>
+    <t>6</t>
   </si>
   <si>
     <t>甜菜</t>
@@ -83,7 +108,7 @@
     <t>0</t>
   </si>
   <si>
-    <t>WaterBottle</t>
+    <t>7</t>
   </si>
   <si>
     <t>矿泉水</t>
@@ -92,7 +117,7 @@
     <t>40</t>
   </si>
   <si>
-    <t>Coconut</t>
+    <t>5</t>
   </si>
   <si>
     <t>椰子</t>
@@ -104,6 +129,21 @@
     <t>20</t>
   </si>
   <si>
+    <t>行类型(setting/resource)</t>
+  </si>
+  <si>
+    <t>配置键</t>
+  </si>
+  <si>
+    <t>配置值</t>
+  </si>
+  <si>
+    <t>刷新道具ID</t>
+  </si>
+  <si>
+    <t>权重</t>
+  </si>
+  <si>
     <t>rowType</t>
   </si>
   <si>
@@ -113,9 +153,6 @@
     <t>value</t>
   </si>
   <si>
-    <t>resourceType</t>
-  </si>
-  <si>
     <t>weight</t>
   </si>
   <si>
@@ -149,12 +186,18 @@
     <t>30</t>
   </si>
   <si>
-    <t>Plastic</t>
+    <t>4</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
+    <t>生存配置键</t>
+  </si>
+  <si>
+    <t>生存配置值</t>
+  </si>
+  <si>
     <t>maxHealth</t>
   </si>
   <si>
@@ -191,15 +234,9 @@
     <t>starveDamage</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>respawnDelay</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>respawnHealth</t>
   </si>
   <si>
@@ -210,6 +247,75 @@
   </si>
   <si>
     <t>respawnThirst</t>
+  </si>
+  <si>
+    <t>配方唯一ID</t>
+  </si>
+  <si>
+    <t>配方显示名</t>
+  </si>
+  <si>
+    <t>输入道具ID</t>
+  </si>
+  <si>
+    <t>输入数量</t>
+  </si>
+  <si>
+    <t>输出道具ID</t>
+  </si>
+  <si>
+    <t>输出数量</t>
+  </si>
+  <si>
+    <t>recipeId</t>
+  </si>
+  <si>
+    <t>inputItemTypeId</t>
+  </si>
+  <si>
+    <t>inputAmount</t>
+  </si>
+  <si>
+    <t>outputItemTypeId</t>
+  </si>
+  <si>
+    <t>outputAmount</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>钩子</t>
+  </si>
+  <si>
+    <t>建造锤</t>
+  </si>
+  <si>
+    <t>木材</t>
+  </si>
+  <si>
+    <t>塑料</t>
+  </si>
+  <si>
+    <t>种植盆</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>晾水器</t>
+  </si>
+  <si>
+    <t>储物箱</t>
+  </si>
+  <si>
+    <t>水杯</t>
+  </si>
+  <si>
+    <t>3,4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1181,12 +1287,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1214,8 +1320,64 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1226,69 +1388,189 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C8" t="s">
         <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1299,134 +1581,151 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
         <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1437,119 +1736,266 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
